--- a/output/pdf_financials_xlsx/INFM.xlsx
+++ b/output/pdf_financials_xlsx/INFM.xlsx
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.079181</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.767882</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.287969</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004368</v>
       </c>
     </row>
     <row r="35">
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.079181</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.767882</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.287969</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004368</v>
       </c>
     </row>
     <row r="37">
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.27138</v>
+        <v>0.192199</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.844127</v>
+        <v>0.07624499999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.357159</v>
+        <v>0.06919</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.013507</v>
+        <v>0.009139</v>
       </c>
     </row>
     <row r="49">
@@ -4540,10 +4540,10 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026111</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.028663</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026111</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.028663</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8110,7 +8110,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
